--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="125">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMTraitement vers la sous-entrée CDA FRCDATraitement puis vers le profil FHIR FRMedicationStatementDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMMedicationUse vers la sous-entrée CDA FRCDATraitement puis vers le profil FHIR FRMedicationStatementDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-traitement</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-use</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement</t>
   </si>
   <si>
-    <t>FRLMTraitement</t>
+    <t>FRLMMedicationUse</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,154 +118,274 @@
     <t>FRCDATraitement</t>
   </si>
   <si>
-    <t>FRLMTraitement.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.id</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.code</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.code</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.note</t>
+    <t>FRLMMedicationUse.header.status</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.header.author[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.author</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.medication</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.consumable</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.reason[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frReferenceInterne</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.renderedDosageInstruction</t>
   </si>
   <si>
     <t>FRCDATraitement.text</t>
   </si>
   <si>
-    <t>FRLMTraitement.status</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occurancePeriod</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[not(@operator='A')]</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.occuranceDateTim</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.effectiveTime[@operator='A']</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.route</t>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.doseQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.rateQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency.numberOfTimes</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.frequency</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency.period</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.effectiveTime.period</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.frequency.additionalInstructions</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.dateOfAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.conditionOfAdministration</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.precondition</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.date[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.eventTime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDATraitement.approachSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.routeOfAdministration</t>
   </si>
   <si>
     <t>FRCDATraitement.routeCode</t>
   </si>
   <si>
-    <t>FRLMTraitement.dosage.site</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.approachSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.dose</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.rate[x]</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.dosage.doseMaximale</t>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.maxDosePerPeriod.quantity</t>
   </si>
   <si>
     <t>FRCDATraitement.maxDoseQuantity</t>
   </si>
   <si>
-    <t>FRLMTraitement.medicament</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.consumable</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.reason</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frReferenceInterne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.prescription</t>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.maxDosePerPeriod.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.maxLifetimeDose</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.derivedFrom[x]</t>
   </si>
   <si>
     <t>FRCDATraitement.entryRelationship:frPrescription</t>
   </si>
   <si>
-    <t>FRLMTraitement.subordinateTreatment</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frTraitementSubordonne</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.instructionsPatient</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.entryRelationship:frInstructionsAuPatient</t>
-  </si>
-  <si>
-    <t>FRLMTraitement.precondition</t>
-  </si>
-  <si>
-    <t>FRCDATraitement.precondition</t>
+    <t>FRLMMedicationUse.note</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-ml-medication-use</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-statement-document</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.identifier</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.category</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.category.text</t>
+    <t>FRMedicationStatementDocument</t>
   </si>
   <si>
     <t>FRMedicationStatementDocument.status</t>
   </si>
   <si>
+    <t>FRLMMedicationUse.treatmentStatus</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.extension:adherence-code</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.medication[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.reason[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.text</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.sequence</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.sequence</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.note</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.patientInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.doseAndRate.rate[x]</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.frequency</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.period</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.additionalInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.event</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.bounds[x]</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationValue</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.duration</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationUnit</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.durationUnit</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationMax</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.durationMax</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.eventTime.eventTimeCode</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.when</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.dosageInstructions.dosageDetails.eventTime.offset</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.offset</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.site</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.route</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerPeriod.numerator</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerPeriod.denominator</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerLifetime</t>
+  </si>
+  <si>
+    <t>FRLMMedicationUse.periodOfUse</t>
+  </si>
+  <si>
     <t>FRMedicationStatementDocument.effectivePeriod</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosage.doseAndRate.doseQuantity</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.timing</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.route</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.site</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.doseAndRate.rateQuantity</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.maxDosePerPeriod</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.medication:FRMedicationDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.reasonReference</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.basedOn:FRMedicationRequestDocument</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosage.additionalInstruction</t>
+    <t>FRMedicationStatementDocument.derivedFrom[x]</t>
   </si>
   <si>
     <t>FRMedicationStatementDocument.note</t>
@@ -520,7 +640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -709,87 +829,204 @@
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E29" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -798,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -820,7 +1057,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -829,7 +1066,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -837,211 +1074,484 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="D24" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E39" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="124">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -274,76 +274,73 @@
     <t>FRMedicationStatementDocument.dosage</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.text</t>
+    <t>FRMedicationStatementDocument.dosage.text</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.sequence</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.sequence</t>
+    <t>FRMedicationStatementDocument.dosage.sequence</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.note</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.patientInstruction</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.doseAndRate.dose[x]</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.doseAndRate.rate[x]</t>
+    <t>FRMedicationStatementDocument.dosage.patientInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.doseAndRate.dose[x]</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.doseAndRate.rate[x]</t>
   </si>
   <si>
     <t>related-to</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.frequency</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.period</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.dayOfWeek</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.timeOfDay</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.additionalInstruction</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.event</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.asNeededCodeableConcept</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.bounds[x]</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.frequency</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.period</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.dayOfWeek</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.timeOfDay</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.additionalInstruction</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.event</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.bounds[x]</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationValue</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.duration</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.duration</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationUnit</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.durationUnit</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.durationUnit</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.duration.durationMax</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.durationMax</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.durationMax</t>
   </si>
   <si>
     <t>source-is-narrower-than-target</t>
@@ -352,31 +349,31 @@
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.eventTime.eventTimeCode</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.when</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.when</t>
   </si>
   <si>
     <t>FRLMMedicationUse.dosageInstructions.dosageDetails.eventTime.offset</t>
   </si>
   <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.timing.repeat.offset</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.site</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.route</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerPeriod.numerator</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerPeriod.denominator</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerAdministration</t>
-  </si>
-  <si>
-    <t>FRMedicationStatementDocument.dosageInstruction.maxDosePerLifetime</t>
+    <t>FRMedicationStatementDocument.dosage.timing.repeat.offset</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.site</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.route</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.maxDosePerPeriod.numerator</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.maxDosePerPeriod.denominator</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.maxDosePerAdministration</t>
+  </si>
+  <si>
+    <t>FRMedicationStatementDocument.dosage.maxDosePerLifetime</t>
   </si>
   <si>
     <t>FRLMMedicationUse.periodOfUse</t>
@@ -1035,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1152,7 +1149,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
@@ -1165,33 +1162,33 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
@@ -1204,7 +1201,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -1217,24 +1214,24 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>95</v>
@@ -1243,7 +1240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -1256,7 +1253,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -1269,7 +1266,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -1282,11 +1279,11 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>99</v>
@@ -1295,11 +1292,11 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>100</v>
@@ -1308,7 +1305,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -1321,7 +1318,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -1334,98 +1331,98 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
-        <v>32</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -1438,7 +1435,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -1451,7 +1448,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -1464,7 +1461,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -1477,7 +1474,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -1490,7 +1487,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -1503,20 +1500,20 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -1529,7 +1526,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -1539,19 +1536,6 @@
         <v>123</v>
       </c>
       <c r="E38" s="2"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="B39" s="2"/>
-      <c r="C39" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D39" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="E39" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication-use</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-medication-use|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-traitement</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-traitement|0.1.0</t>
   </si>
   <si>
     <t>FRLMMedicationUse</t>
@@ -244,10 +244,10 @@
     <t>FRLMMedicationUse.note</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-ml-medication-use</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-statement-document</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-ml-medication-use</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-statement-document|0.1.0</t>
   </si>
   <si>
     <t>FRMedicationStatementDocument</t>

--- a/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
+++ b/main/ig/FRMedicationStatementLMCDAFHIR.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
